--- a/data/trans_bre/IP07_C13_R_2023-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP07_C13_R_2023-Estudios-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,187 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>0,05</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>1,54</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-9,84</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1,26%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>14,71%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-57,65%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.0504133679468402</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>1.537786863666929</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-9.841212398772651</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0.0125973987860679</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>0.1470585574618265</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>-0.57647167999694</v>
+      </c>
+      <c r="J4" s="6" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-6,06; 6,59</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-9,42; 12,83</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-22,85; 3,25</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-60,87; 281,49</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-90,28; 62,58</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-6.063869128715671</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-9.423230838477711</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-22.85430976125149</v>
+      </c>
+      <c r="F5" s="5" t="inlineStr"/>
+      <c r="G5" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.6086988782502677</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.9028478610556699</v>
+      </c>
+      <c r="J5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>6.587945306034859</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>12.83143346866559</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>3.249233257466201</v>
+      </c>
+      <c r="F6" s="5" t="inlineStr"/>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="n">
+        <v>2.814934569164853</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>0.6258456431436705</v>
+      </c>
+      <c r="J6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Secundarios</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>1,56</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>5,87</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-0,53</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>3,54</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>37,65%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>49,36%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-5,66%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>159,58%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-1,86; 5,12</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>0,45; 10,91</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-4,87; 3,73</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>0,2; 7,87</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-33,7; 193,48</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>3,0; 118,84</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-41,78; 51,58</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-14,93; 834,89</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>1.562709073238925</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>5.868775722661056</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-0.5345399889760349</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>3.539685538371458</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.3765477156379073</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.4935524072778535</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>-0.05659677923562144</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>1.595777965984964</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>1,23</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-2,32</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>2,11</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-1,13</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>30,54%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-19,53%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>24,77%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-1.855379558718822</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.4468946155713941</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-4.866190083826108</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>0.2018591517752679</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.3370385158510124</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>0.02997951235888864</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.4178221181021051</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.1493299514488919</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-5,54; 7,76</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-12,11; 6,73</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-6,25; 9,71</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-5,7; 0,0</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 916,9</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-71,95; 108,98</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-53,02; 178,36</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>5.115955843342888</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>10.91075544150147</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>3.726521467270272</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>7.873952886076857</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>1.934842420928832</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>1.188380835150966</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0.515801625340726</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>8.348933013224467</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,97 +807,193 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>1,26</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>3,52</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-0,93</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2,29</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>30,59%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>30,1%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-9,24%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>122,78%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>1.225015420858837</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-2.324050487781753</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>2.114984282266599</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-1.133956069953333</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0.3053847143257902</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.1953217897947032</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>0.2476547633830349</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-1,23; 4,05</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-0,82; 7,88</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-4,68; 2,94</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-0,12; 5,92</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-25,9; 139,95</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-7,65; 77,65</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-38,98; 36,91</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-21,64; 663,43</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-5.544879229384327</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-12.10915841194963</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-6.254480950679947</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-5.703350011435244</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.7194943100077578</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.530179252247455</v>
+      </c>
+      <c r="J11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>7.75965764880546</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>6.730917877372914</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>9.714451327801187</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>9.169016595952591</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>1.089754844348992</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>1.783611329981258</v>
+      </c>
+      <c r="J12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>1.256523321234811</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>3.519862792742411</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-0.9290477197198401</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>2.291262253806713</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.3059147818965136</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.3010424907979359</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>-0.09244894810078427</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>1.227772544485084</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-1.232059047718384</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-0.821895554488716</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-4.680261354169793</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-0.121394541852949</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.2589787479455485</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.07650656857161593</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.389843931856632</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.2163652148189736</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>4.054320322328077</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>7.876324349366472</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>2.939975814443715</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>5.919708239842252</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>1.399483390345514</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.7765316556841709</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.3690811556803936</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>6.634316962236261</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1008,13 +1001,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
